--- a/frontend/public/templates/modelo_210_alquiler_turistico.xlsx
+++ b/frontend/public/templates/modelo_210_alquiler_turistico.xlsx
@@ -852,7 +852,7 @@
         <v>16</v>
       </c>
       <c r="B3" s="7">
-        <f>'Gastos Deducibles'!G2</f>
+        <f>'Gastos Deducibles'!G2+'Ingresos Modelo 210'!I2</f>
         <v>0</v>
       </c>
     </row>
